--- a/data/trans_orig/IQ17B_M_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ17B_M_R-Habitat-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,72; 8,17</t>
+          <t>4,72; 8,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,27; 5,81</t>
+          <t>4,29; 5,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,39; 8,51</t>
+          <t>5,38; 8,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,27; 13,4</t>
+          <t>8,32; 13,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,1; 7,21</t>
+          <t>5,15; 7,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,32; 7,78</t>
+          <t>5,37; 7,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,67; 6,51</t>
+          <t>4,75; 6,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,63; 13,93</t>
+          <t>6,5; 14,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,21; 7,13</t>
+          <t>5,23; 7,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,01; 6,71</t>
+          <t>5,02; 6,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,28; 7,12</t>
+          <t>5,3; 7,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,77; 12,3</t>
+          <t>7,68; 12,01</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 8,08</t>
+          <t>5,49; 8,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,21; 5,62</t>
+          <t>4,2; 5,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,04; 6,66</t>
+          <t>5,04; 6,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,15; 9,24</t>
+          <t>7,13; 9,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,21; 7,29</t>
+          <t>5,26; 7,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 8,74</t>
+          <t>5,42; 8,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,73; 7,81</t>
+          <t>5,62; 7,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,43; 11,03</t>
+          <t>8,45; 10,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,62; 7,42</t>
+          <t>5,54; 7,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,05; 6,84</t>
+          <t>5,07; 6,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,59; 6,96</t>
+          <t>5,54; 6,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,14; 9,78</t>
+          <t>8,07; 9,74</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 6,96</t>
+          <t>5,08; 6,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,31; 5,97</t>
+          <t>4,36; 5,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,74; 8,26</t>
+          <t>5,79; 8,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,89; 9,0</t>
+          <t>5,83; 8,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,84; 8,74</t>
+          <t>5,84; 8,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 6,55</t>
+          <t>4,4; 6,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,98; 8,79</t>
+          <t>5,87; 8,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,63; 17,23</t>
+          <t>7,49; 17,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,67; 7,33</t>
+          <t>5,75; 7,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 5,91</t>
+          <t>4,55; 5,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,13; 8,06</t>
+          <t>6,18; 8,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,03; 11,7</t>
+          <t>7,1; 12,75</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,04; 8,24</t>
+          <t>5,96; 8,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,01; 7,51</t>
+          <t>5,02; 7,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,0; 6,35</t>
+          <t>5,01; 6,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,15; 9,27</t>
+          <t>7,16; 9,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 7,3</t>
+          <t>5,48; 7,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,95; 6,62</t>
+          <t>4,96; 6,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,58; 7,38</t>
+          <t>5,56; 7,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,67; 10,86</t>
+          <t>7,74; 10,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,99; 7,4</t>
+          <t>5,95; 7,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,19; 6,7</t>
+          <t>5,22; 6,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,48; 6,59</t>
+          <t>5,45; 6,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,75; 9,67</t>
+          <t>7,7; 9,5</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,83; 7,06</t>
+          <t>5,83; 7,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,78; 5,67</t>
+          <t>4,81; 5,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,65; 6,65</t>
+          <t>5,62; 6,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,46; 8,98</t>
+          <t>7,55; 8,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,81; 6,88</t>
+          <t>5,8; 6,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,44; 6,63</t>
+          <t>5,42; 6,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,88; 6,97</t>
+          <t>5,9; 6,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,53; 11,4</t>
+          <t>8,48; 11,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,95; 6,85</t>
+          <t>5,95; 6,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,05</t>
+          <t>5,22; 5,96</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,93; 6,67</t>
+          <t>5,91; 6,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,18; 9,71</t>
+          <t>8,21; 9,77</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ17B_M_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ17B_M_R-Habitat-trans_orig.xlsx
@@ -526,13 +526,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores en función del número de meses de su última consulta al médico (tasa de respuesta: 91,3%)</t>
+          <t>Tiempo medio en meses desde la última consulta médica por algo que le pasaba a su hijo/a (tasa de respuesta: 91,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,08</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6,37</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5,57</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9,05</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5,84</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,98</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>6,55</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9,79</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,08</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,37</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,57</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,87</t>
+          <t>10,04</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,29</t>
+          <t>9,53</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,72; 8,22</t>
+          <t>5,1; 7,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 5,79</t>
+          <t>5,31; 7,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,38; 8,38</t>
+          <t>4,75; 6,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,32; 13,34</t>
+          <t>6,95; 14,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 7,33</t>
+          <t>4,69; 8,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,37; 7,82</t>
+          <t>4,27; 5,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,75; 6,66</t>
+          <t>5,5; 8,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,5; 14,12</t>
+          <t>8,45; 14,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,23; 7,16</t>
+          <t>5,2; 7,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,54</t>
+          <t>5,03; 6,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,3; 7,09</t>
+          <t>5,32; 7,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,68; 12,01</t>
+          <t>8,09; 12,26</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,08</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6,35</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6,53</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9,91</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>6,45</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>4,78</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>5,74</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8,11</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,08</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,35</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,53</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,51</t>
+          <t>8,44</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,86</t>
+          <t>9,21</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,49; 8,37</t>
+          <t>5,28; 7,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 5,63</t>
+          <t>5,41; 8,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,04; 6,77</t>
+          <t>5,58; 7,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,13; 9,21</t>
+          <t>8,78; 11,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,26; 7,4</t>
+          <t>5,47; 8,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,58</t>
+          <t>4,24; 5,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,62; 7,83</t>
+          <t>5,0; 6,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,45; 10,95</t>
+          <t>7,55; 9,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,54; 7,22</t>
+          <t>5,57; 7,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 6,9</t>
+          <t>5,05; 6,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,54; 6,94</t>
+          <t>5,59; 6,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,07; 9,74</t>
+          <t>8,47; 10,22</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,92</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,21</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7,1</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10,08</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5,91</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,98</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6,9</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,93</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,92</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,21</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,1</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,31</t>
+          <t>7,02</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,66</t>
+          <t>8,56</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,08; 6,95</t>
+          <t>5,99; 8,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 5,85</t>
+          <t>4,42; 6,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,79; 8,39</t>
+          <t>5,93; 8,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,83; 8,78</t>
+          <t>7,64; 15,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,84; 8,59</t>
+          <t>5,1; 6,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,4; 6,57</t>
+          <t>4,34; 5,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 8,61</t>
+          <t>5,83; 8,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 17,01</t>
+          <t>6,0; 9,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,75; 7,41</t>
+          <t>5,75; 7,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,55; 5,83</t>
+          <t>4,57; 5,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,18; 8,1</t>
+          <t>6,14; 8,08</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,1; 12,75</t>
+          <t>7,11; 11,36</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,27</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,31</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9,25</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6,93</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,87</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5,63</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,09</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,27</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,7</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,31</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,09</t>
+          <t>8,37</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,61</t>
+          <t>8,8</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,96; 8,3</t>
+          <t>5,44; 7,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,02; 7,43</t>
+          <t>4,98; 6,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,01; 6,35</t>
+          <t>5,55; 7,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,16; 9,25</t>
+          <t>7,88; 10,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,48; 7,25</t>
+          <t>6,0; 8,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 6,68</t>
+          <t>5,03; 7,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,56; 7,36</t>
+          <t>4,96; 6,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,74; 10,87</t>
+          <t>7,4; 9,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,95; 7,39</t>
+          <t>5,94; 7,42</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,22; 6,65</t>
+          <t>5,12; 6,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 6,56</t>
+          <t>5,44; 6,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,7; 9,5</t>
+          <t>7,96; 9,76</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6,31</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,93</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6,41</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9,63</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>6,38</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>5,19</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>6,11</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8,13</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,31</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,93</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,41</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,47</t>
+          <t>8,4</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,84</t>
+          <t>9,03</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,83; 7,15</t>
+          <t>5,82; 6,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,81; 5,72</t>
+          <t>5,39; 6,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,62; 6,64</t>
+          <t>5,91; 6,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,55; 8,97</t>
+          <t>8,66; 11,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,8; 6,94</t>
+          <t>5,86; 7,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,42; 6,61</t>
+          <t>4,77; 5,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,9; 6,98</t>
+          <t>5,65; 6,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,48; 11,31</t>
+          <t>7,81; 9,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,95; 6,81</t>
+          <t>5,96; 6,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,22; 5,96</t>
+          <t>5,25; 6,01</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 6,65</t>
+          <t>5,89; 6,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,21; 9,77</t>
+          <t>8,42; 9,85</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ17B_M_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ17B_M_R-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>6,08</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6,37</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5,57</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9,05</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,84</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,98</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,55</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10,04</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5,96</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5,72</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6,05</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>9,53</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>6.076779568009998</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>6.374240646151282</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>5.569225396909769</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>9.047926283092641</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>5.835796835176652</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>4.98004904186166</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>6.551889245775153</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>10.04385193763301</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>5.962809791991495</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>5.723553840935332</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>6.051510898733432</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>9.531834641097808</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>5,1; 7,17</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5,31; 7,76</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4,75; 6,64</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6,95; 14,15</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>4,69; 8,14</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4,27; 5,81</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5,5; 8,47</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8,45; 14,07</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5,2; 7,2</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5,03; 6,5</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5,32; 7,18</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>8,09; 12,26</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>5.097083177680547</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>5.307203814348362</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>4.754382293465641</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>6.948687868333364</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>4.692895584893051</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>4.265738873677358</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>5.49599817876804</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>8.446916169333416</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>5.201752329191047</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>5.034880118879878</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>5.31672399780336</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>8.091802407288096</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7.17225515166364</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>7.763054839205354</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.638569102202463</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>14.14580633930314</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>8.142876886135381</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>5.808524781463244</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>8.472022143400695</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>14.06552289804679</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>7.202234403086496</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>6.501164547886974</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>7.181151975653508</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>12.26469386391373</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>6,08</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>6,35</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6,53</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9,91</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,45</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,78</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,74</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8,44</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>6,25</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>5,59</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6,16</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,21</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>5,28; 7,51</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5,41; 8,8</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5,58; 7,82</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8,78; 11,44</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5,47; 8,39</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,24; 5,53</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,0; 6,72</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7,55; 9,61</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5,57; 7,21</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5,05; 6,73</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5,59; 6,94</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,47; 10,22</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>6.077183687431025</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>6.349034685361882</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>6.534578522840072</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>9.906933568804538</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>6.449548958969006</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>4.777922308030291</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>5.742765326974112</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>8.435496234088543</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>6.254357535119428</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>5.589736433093963</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>6.163198119742056</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>9.210139912696812</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>6,92</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5,21</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7,1</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10,08</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,91</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,98</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,9</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>7,02</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>6,41</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>5,1</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>7,01</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>8,56</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>5.280358925365923</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>5.41146919371005</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>5.58468861625941</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>8.778295316873839</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>5.473506043636545</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>4.242046514802826</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>4.997036796692404</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>7.553036690808951</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>5.570255720994275</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>5.045877664571784</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>5.588245404983486</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>8.471226255730752</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>5,99; 8,65</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>4,42; 6,62</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>5,93; 8,66</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>7,64; 15,86</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>5,1; 6,93</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>4,34; 5,96</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>5,83; 8,58</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>6,0; 9,23</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>5,75; 7,34</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>4,57; 5,94</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>6,14; 8,08</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>7,11; 11,36</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>7.509972571275956</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>8.79648138879398</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>7.818471499012199</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>11.44009422535557</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>8.388635733982118</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>5.529586042049452</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>6.720661416130929</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>9.606237807943787</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>7.208239643640023</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>6.731537871877423</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>6.935340444565257</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>10.21700851078863</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>6,27</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5,7</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6,31</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,25</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,93</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,87</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,63</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8,37</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6,62</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5,78</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5,96</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,8</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>6.922788348188607</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>5.213385416869579</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>7.101790545432856</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>10.08113176877914</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>5.905962105158861</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>4.979278121256333</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>6.903087856903181</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>7.024539256287603</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>6.411111197550898</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>5.09767316890456</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>7.007143668335174</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>8.55617337157191</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>5,44; 7,3</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>4,98; 6,65</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5,55; 7,34</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7,88; 10,98</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>6,0; 8,31</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5,03; 7,64</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,96; 6,4</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7,4; 9,52</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>5,94; 7,42</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>5,12; 6,54</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>5,44; 6,54</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>7,96; 9,76</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>5.990087746204445</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>4.423166975434053</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>5.927236982744344</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>7.636192831497785</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>5.099524008464636</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>4.337573261978635</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>5.832143505714734</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>5.997317630107026</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>5.746692417914089</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>4.571346656303103</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>6.143985026986803</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>7.114025821082998</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>8.649390106631081</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.617260296427671</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>8.661664237463011</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>15.86121603248946</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>6.932409538133703</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>5.964020786016618</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>8.581873172494033</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>9.225668493098295</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>7.342610491115784</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>5.940807736553936</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>8.076720908406072</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>11.35734722007821</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>6.267261006419124</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>5.701967365281073</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>6.313648882291867</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>9.245658555553844</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>6.926533699131634</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>5.867762905450514</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>5.630296168095061</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>8.366813618627633</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>6.621965154594377</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>5.782565928703121</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>5.962517260605255</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>8.801201672519943</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>5.438753592599754</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>4.978651356020524</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>5.548771321039993</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>7.878739691332388</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>6.001136048510323</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>5.025406001727601</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>4.962821964638174</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>7.400768372400806</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>5.938013752114078</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>5.11930689727422</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>5.443544117474412</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>7.960039797631802</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>7.30160944319577</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>6.646836417361615</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>7.343034336637783</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>10.9838227989447</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>8.31224596717375</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>7.644531824754672</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>6.404831030972724</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>9.515658156213204</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>7.424901610885546</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>6.542581780498553</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>6.544275238466426</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>9.763856055043622</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>6,31</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>5,93</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6,41</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9,63</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,38</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,19</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,11</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8,4</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>6,34</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>5,57</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>6,26</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,03</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>5,82; 6,89</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5,39; 6,64</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5,91; 6,95</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8,66; 11,12</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5,86; 7,04</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,77; 5,69</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,65; 6,67</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7,81; 9,31</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5,96; 6,81</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5,25; 6,01</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5,89; 6,62</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,42; 9,85</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>6.313500401941613</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>5.927250755169738</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>6.409716475155274</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>9.626501739644102</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>6.375251424384292</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>5.187268300719906</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>6.112714209750386</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>8.398583892350468</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>6.34440587214184</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>5.569766014913752</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>6.264766149745702</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>9.025558523926851</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>5.823207279982057</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>5.387702943318156</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>5.910952614123493</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>8.657597770561066</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>5.861214706991507</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>4.770470046331008</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>5.650762711975142</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>7.808656220437176</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>5.963507821291759</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>5.247565463430572</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>5.892573012397035</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>8.421109842676843</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>6.889023733518772</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>6.644418648348846</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>6.945046292950738</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>11.115460547874</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>7.043998315793036</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>5.687531049695793</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>6.669640298919225</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>9.311771362622764</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>6.814682427607019</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>6.00897061354271</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>6.616622732066278</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>9.852484715821992</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
